--- a/Project/Tuntiseuranta.xlsx
+++ b/Project/Tuntiseuranta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iryna.sula\Documents\git\unity-irensula\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3670B19-6DC9-4965-B327-815E392BB26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CFC34E-51FD-4967-913E-3FED59470D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3975" yWindow="3015" windowWidth="18900" windowHeight="10965" xr2:uid="{A35A2CE8-B48B-4FB7-BA14-B4605E3E4430}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>Päiväys</t>
   </si>
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -450,6 +450,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -462,6 +463,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -573,9 +575,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -2684,346 +2683,331 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
+      <c r="A2" s="20">
         <v>45939</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="22">
         <v>7.5</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="23">
         <v>6</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="25" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="24">
+      <c r="A3" s="26">
         <v>45951</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="28">
         <v>4</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <v>4</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="31">
+      <c r="A4" s="33">
         <v>45952</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="35">
         <v>6</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="35">
         <v>6</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="36"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="37">
+      <c r="A5" s="39">
         <v>45954</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="41">
         <v>8</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="42">
         <v>8</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="45" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="20">
         <v>45958</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="22">
         <v>4</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="23">
         <v>4</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="45"/>
+      <c r="G6" s="47"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="34">
         <v>45959</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="35">
         <v>6.5</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="48">
         <v>6.5</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="48"/>
+      <c r="G7" s="50"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="34">
         <v>45961</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="35">
         <v>7</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="35">
         <v>7</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="37"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
+      <c r="A9" s="34">
         <v>45965</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="35">
         <v>6.5</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="35">
         <v>6.5</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="51"/>
+      <c r="G9" s="53"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="34">
         <v>45966</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="35">
         <v>7</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="35">
         <v>7</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>45979</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <v>6.5</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="54">
         <v>6.5</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <v>45980</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <v>7</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <v>7</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="54">
-        <v>45987</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="52">
-        <v>7</v>
-      </c>
-      <c r="D13" s="52">
-        <v>7</v>
-      </c>
-      <c r="E13" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="53"/>
-      <c r="G13" s="13"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="54"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="13"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="12"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="13"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="12"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="56">
+      <c r="C20" s="7">
         <f>SUM(C2:C19)</f>
-        <v>77</v>
-      </c>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3148,144 +3132,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+      <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:3" ht="126" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="8">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="9"/>
     </row>
     <row r="5" spans="1:3" ht="63" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
     </row>
     <row r="7" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
     </row>
     <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="9"/>
     </row>
     <row r="11" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="8">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>8</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="A14" s="9"/>
     </row>
     <row r="15" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>10</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
+      <c r="A19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
+      <c r="A20" s="9"/>
       <c r="E20">
         <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E21">
@@ -3299,46 +3283,46 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="19" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="19" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3358,17 +3342,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aee9339b-7095-4861-9341-62921a98955a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="660b6cfa-6e14-4451-aa9c-04f8e527d3c1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x0101001A3B01681A17E041A19037BA597D1C86" ma:contentTypeVersion="12" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="ca537cae08f959cd75b47a6fdb2cba50">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aee9339b-7095-4861-9341-62921a98955a" xmlns:ns3="660b6cfa-6e14-4451-aa9c-04f8e527d3c1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="113a82006141fe5afd4730f10724ab16" ns2:_="" ns3:_="">
     <xsd:import namespace="aee9339b-7095-4861-9341-62921a98955a"/>
@@ -3563,6 +3536,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aee9339b-7095-4861-9341-62921a98955a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="660b6cfa-6e14-4451-aa9c-04f8e527d3c1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F54F30-26E5-472C-92E0-CAD89654AA37}">
   <ds:schemaRefs>
@@ -3572,17 +3556,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8DC34F-B8C7-4EBB-B5AA-5C1A72982195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="aee9339b-7095-4861-9341-62921a98955a"/>
-    <ds:schemaRef ds:uri="660b6cfa-6e14-4451-aa9c-04f8e527d3c1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7EB30EA-D46C-45FA-8FBE-6FF8366F3CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3599,4 +3572,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8DC34F-B8C7-4EBB-B5AA-5C1A72982195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="aee9339b-7095-4861-9341-62921a98955a"/>
+    <ds:schemaRef ds:uri="660b6cfa-6e14-4451-aa9c-04f8e527d3c1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>